--- a/site-data.xlsx
+++ b/site-data.xlsx
@@ -1551,16 +1551,16 @@
         <v>transformation-1</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>video</v>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>video</v>
       </c>
       <c r="I2" t="str">
-        <v/>
+        <v>https://res.cloudinary.com/dvygreryl/video/upload/v1782240561/dsbs/transformations/transformation-1/before.mp4</v>
       </c>
       <c r="J2" t="str">
-        <v/>
+        <v>https://res.cloudinary.com/dvygreryl/video/upload/v1782240557/dsbs/transformations/transformation-1/after.mp4</v>
       </c>
     </row>
     <row r="3">
@@ -1583,16 +1583,16 @@
         <v>transformation-2</v>
       </c>
       <c r="G3" t="str">
-        <v/>
+        <v>video</v>
       </c>
       <c r="H3" t="str">
-        <v/>
+        <v>video</v>
       </c>
       <c r="I3" t="str">
-        <v/>
+        <v>https://res.cloudinary.com/dvygreryl/video/upload/v1782240567/dsbs/transformations/transformation-2/before.mp4</v>
       </c>
       <c r="J3" t="str">
-        <v/>
+        <v>https://res.cloudinary.com/dvygreryl/video/upload/v1782240564/dsbs/transformations/transformation-2/after.mp4</v>
       </c>
     </row>
     <row r="4">
@@ -1615,16 +1615,16 @@
         <v>transformation-3</v>
       </c>
       <c r="G4" t="str">
-        <v/>
+        <v>video</v>
       </c>
       <c r="H4" t="str">
-        <v/>
+        <v>video</v>
       </c>
       <c r="I4" t="str">
-        <v/>
+        <v>https://res.cloudinary.com/dvygreryl/video/upload/v1782240579/dsbs/transformations/transformation-3/before.mp4</v>
       </c>
       <c r="J4" t="str">
-        <v/>
+        <v>https://res.cloudinary.com/dvygreryl/video/upload/v1782240576/dsbs/transformations/transformation-3/after.mp4</v>
       </c>
     </row>
   </sheetData>

--- a/site-data.xlsx
+++ b/site-data.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="309">
   <si>
     <t>HOW TO UPDATE YOUR WEBSITE</t>
   </si>
@@ -1329,7 +1329,7 @@
   <dimension ref="A1:A9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="51.857142857142854" customWidth="1"/>
+    <col min="1" max="1" width="42.142857142857146" customWidth="1"/>
     <col min="2" max="24" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1491,8 +1491,7 @@
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="55.857142857142854" customWidth="1"/>
-    <col min="2" max="2" width="44.142857142857146" customWidth="1"/>
+    <col min="1" max="2" width="42.142857142857146" customWidth="1"/>
     <col min="3" max="24" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1798,7 +1797,7 @@
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="38.285714285714285" customWidth="1"/>
-    <col min="2" max="2" width="59.714285714285715" customWidth="1"/>
+    <col min="2" max="2" width="42.142857142857146" customWidth="1"/>
     <col min="3" max="24" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1838,8 +1837,8 @@
       <c r="A5" t="s">
         <v>15</v>
       </c>
-      <c r="B5" t="s">
-        <v>14</v>
+      <c r="B5">
+        <v>7764013710</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
